--- a/tasks/finalpool/sf-support-industry-fetch-excel-word/groundtruth_workspace/Support_Benchmark_Report.xlsx
+++ b/tasks/finalpool/sf-support-industry-fetch-excel-word/groundtruth_workspace/Support_Benchmark_Report.xlsx
@@ -466,7 +466,7 @@
         <v>6466</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="D3" t="n">
         <v>20.5</v>
@@ -482,7 +482,7 @@
         <v>15774</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>12.3</v>
       </c>
       <c r="D4" t="n">
         <v>49.9</v>
@@ -498,7 +498,7 @@
         <v>9348</v>
       </c>
       <c r="C5" t="n">
-        <v>15</v>
+        <v>25.8</v>
       </c>
       <c r="D5" t="n">
         <v>29.6</v>
@@ -552,13 +552,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.5</v>
+        <v>15</v>
       </c>
       <c r="C2" t="n">
         <v>5.2</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -573,17 +573,17 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="C3" t="n">
         <v>87.5</v>
       </c>
       <c r="D3" t="n">
-        <v>-5.5</v>
+        <v>12.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
     </row>
@@ -594,13 +594,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="C4" t="n">
         <v>4.1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.3</v>
+        <v>-0.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -668,7 +668,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3.3 hours above industry average</t>
+          <t>9.8 hours above industry average</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -680,34 +680,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Resolution Rate</t>
+          <t>Customer Satisfaction</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>5.5% below industry average</t>
+          <t>0.8 points below benchmark</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Enhance knowledge base and training</t>
+          <t>Improve follow-up processes</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Customer Satisfaction</t>
+          <t>Resolution Rate</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.3 points below benchmark</t>
+          <t>Above benchmark by 12.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Improve follow-up processes</t>
+          <t>Maintain current resolution practices</t>
         </is>
       </c>
     </row>
